--- a/artfynd/A 35775-2022 artfynd.xlsx
+++ b/artfynd/A 35775-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439672</v>
       </c>
       <c r="B2" t="n">
-        <v>108151</v>
+        <v>108154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439662</v>
       </c>
       <c r="B3" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35775-2022 artfynd.xlsx
+++ b/artfynd/A 35775-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439672</v>
       </c>
       <c r="B2" t="n">
-        <v>108154</v>
+        <v>108155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439662</v>
       </c>
       <c r="B3" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35775-2022 artfynd.xlsx
+++ b/artfynd/A 35775-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439672</v>
       </c>
       <c r="B2" t="n">
-        <v>108155</v>
+        <v>108160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439662</v>
       </c>
       <c r="B3" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35775-2022 artfynd.xlsx
+++ b/artfynd/A 35775-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439672</v>
       </c>
       <c r="B2" t="n">
-        <v>108160</v>
+        <v>108162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439662</v>
       </c>
       <c r="B3" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35775-2022 artfynd.xlsx
+++ b/artfynd/A 35775-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439672</v>
       </c>
       <c r="B2" t="n">
-        <v>108162</v>
+        <v>108168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439662</v>
       </c>
       <c r="B3" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35775-2022 artfynd.xlsx
+++ b/artfynd/A 35775-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439672</v>
       </c>
       <c r="B2" t="n">
-        <v>108168</v>
+        <v>108170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439662</v>
       </c>
       <c r="B3" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35775-2022 artfynd.xlsx
+++ b/artfynd/A 35775-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439672</v>
       </c>
       <c r="B2" t="n">
-        <v>108170</v>
+        <v>108171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439662</v>
       </c>
       <c r="B3" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
